--- a/data/trans_orig/IP1001-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1001-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83050</t>
+          <t>82785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89001</t>
+          <t>89509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80300</t>
+          <t>80627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86165</t>
+          <t>86153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165749</t>
+          <t>165735</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174405</t>
+          <t>174323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>17331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30714</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398876</t>
+          <t>398756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409376</t>
+          <t>409508</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459420</t>
+          <t>460061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470141</t>
+          <t>470293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862364</t>
+          <t>862559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>877556</t>
+          <t>877944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163345</t>
+          <t>163161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171561</t>
+          <t>171340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147034</t>
+          <t>147763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155508</t>
+          <t>155460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314174</t>
+          <t>313811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325181</t>
+          <t>325565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26579</t>
+          <t>27321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>29996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51874</t>
+          <t>51112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>652870</t>
+          <t>652026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>667138</t>
+          <t>666395</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>695395</t>
+          <t>694653</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709108</t>
+          <t>708824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1351121</t>
+          <t>1351883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1372135</t>
+          <t>1372999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84769</t>
+          <t>83401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90583</t>
+          <t>90559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74084</t>
+          <t>74154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82455</t>
+          <t>82461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162131</t>
+          <t>162006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172048</t>
+          <t>171853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433474</t>
+          <t>433729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>444249</t>
+          <t>444410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475252</t>
+          <t>475271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486371</t>
+          <t>485915</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>913800</t>
+          <t>912667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928408</t>
+          <t>928763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163127</t>
+          <t>162803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161120</t>
+          <t>161377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>169365</t>
+          <t>169355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>326224</t>
+          <t>326278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>334244</t>
+          <t>334256</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>28168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24357</t>
+          <t>25055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>45019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>686167</t>
+          <t>686636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>698439</t>
+          <t>699072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>719595</t>
+          <t>719949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733612</t>
+          <t>734333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1410206</t>
+          <t>1410026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1430688</t>
+          <t>1429990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50878</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57758</t>
+          <t>57571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63819</t>
+          <t>64178</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117834</t>
+          <t>117803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125499</t>
+          <t>125509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456051</t>
+          <t>455999</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>466631</t>
+          <t>466748</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468299</t>
+          <t>468715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480342</t>
+          <t>480846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>928527</t>
+          <t>928293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944128</t>
+          <t>944846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167931</t>
+          <t>167927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172169</t>
+          <t>172174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177927</t>
+          <t>178420</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185505</t>
+          <t>185543</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348570</t>
+          <t>348330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>356953</t>
+          <t>357034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>27885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>44912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>680332</t>
+          <t>680566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>693939</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>718119</t>
+          <t>716959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>732128</t>
+          <t>731517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1403208</t>
+          <t>1404303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1423061</t>
+          <t>1423415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50710</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55664</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61481</t>
+          <t>61480</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108783</t>
+          <t>109562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115766</t>
+          <t>115899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>39709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443699</t>
+          <t>443529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>454655</t>
+          <t>454265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489080</t>
+          <t>488811</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504608</t>
+          <t>505216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936883</t>
+          <t>936604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>956554</t>
+          <t>956294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141751</t>
+          <t>141729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148198</t>
+          <t>148291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164766</t>
+          <t>161217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181670</t>
+          <t>181649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310020</t>
+          <t>309142</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328726</t>
+          <t>328440</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56304</t>
+          <t>58098</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>641565</t>
+          <t>642347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>654893</t>
+          <t>655221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>721801</t>
+          <t>720777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744728</t>
+          <t>743244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1369591</t>
+          <t>1367797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1396023</t>
+          <t>1394726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1001-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1001-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6650</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3912</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8082</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7864</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>84098</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80195</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86151</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>86955</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82785</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>89509</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>83003</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>89530</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>84098</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>80627</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86153</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165735</t>
+          <t>165448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174323</t>
+          <t>173893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>10963</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6152</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16913</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>10973</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6579</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17331</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17295</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10963</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6698</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16930</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30519</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>466028</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>460078</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>470839</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>611</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>405114</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>398756</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>409508</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>398792</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>409488</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,36%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>466028</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>460061</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>470293</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862559</t>
+          <t>863085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>877944</t>
+          <t>877491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10952</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>5650</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2726</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10905</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2629</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10973</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5567</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2678</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10375</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>18924</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152571</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>147186</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>155471</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>168416</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>163161</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>171340</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>163093</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>171437</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152571</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>147763</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>155460</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313811</t>
+          <t>313281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325565</t>
+          <t>324953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13446</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27793</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20535</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14626</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28995</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14301</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29054</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19277</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13150</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>27321</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29996</t>
+          <t>31636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>51250</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>702697</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>694181</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>708528</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>987</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>660486</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>652026</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>666395</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>651967</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>666720</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,98%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1056</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>702697</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>694653</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>708824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1351883</t>
+          <t>1351745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1372999</t>
+          <t>1371359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3629</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9384</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3535</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1330</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8488</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3629</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9383</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>79908</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>74153</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82848</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88354</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>83401</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>90559</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>84120</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>90594</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>79908</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>74154</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82461</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162006</t>
+          <t>161768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171853</t>
+          <t>172014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11218</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6674</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17264</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9470</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5290</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15971</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5414</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15392</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11218</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7104</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17748</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>28884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>481801</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>475755</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>486345</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>638</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>440230</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>433729</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>444410</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>434308</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>444286</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,89%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>481801</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>475271</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>485915</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>912667</t>
+          <t>913835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928763</t>
+          <t>928661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>493019</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>493019</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>493019</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>493019</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>493019</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>493019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5166</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2219</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10242</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2537</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5166</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2206</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10184</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166395</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>161319</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>169342</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164897</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162803</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>163197</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166395</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>161377</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>169355</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>469</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>326278</t>
+          <t>326099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>334256</t>
+          <t>334363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13791</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28380</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13448</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7856</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20292</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8232</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20330</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13784</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>28168</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25055</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45019</t>
+          <t>43822</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>728104</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>719737</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>734326</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>999</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>693480</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>686636</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>699072</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>686598</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>698696</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,1%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1038</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>728104</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>719949</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>734333</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1410026</t>
+          <t>1411223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1429990</t>
+          <t>1429999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>748117</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>748117</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>748117</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>748117</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>748117</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>748117</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4278</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4112</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1807</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9171</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1868</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8753</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,93%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67329</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64336</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55266</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50207</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57571</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50625</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57510</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,07%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67329</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>64178</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117803</t>
+          <t>117685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125509</t>
+          <t>125500</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13212</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8412</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19790</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9910</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5542</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16291</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5946</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16505</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,1%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13212</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7889</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>20020</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>15716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>475523</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>468945</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>480323</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>462380</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>455999</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>466748</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>455785</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>466344</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,9%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>475523</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>468715</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>480846</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>928293</t>
+          <t>929135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944846</t>
+          <t>945309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4757</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9355</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1738</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4776</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4721</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4757</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9075</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>182738</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>178140</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>185527</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>170965</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>167927</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>172174</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>167982</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>172156</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>182738</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>178420</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>185543</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348330</t>
+          <t>348248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357034</t>
+          <t>356992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13025</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27863</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15761</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10516</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23805</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10036</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23232</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19253</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13327</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>27885</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25800</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44912</t>
+          <t>46378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>725591</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>716981</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>731819</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1038</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>688610</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>680566</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>693855</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>681139</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>694335</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>725591</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>716959</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>731517</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1404303</t>
+          <t>1402837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1423415</t>
+          <t>1422810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3827</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4059</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6867</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>54349</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50572</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56210</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53933</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50851</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>45955</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42699</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59691</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55137</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61480</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>88,92%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>148</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>113625</t>
+          <t>100304</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109562</t>
+          <t>96003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115899</t>
+          <t>102602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17481</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11035</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25791</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9894</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5429</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16165</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27808</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28425</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39709</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>458197</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>449887</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>464643</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>449800</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>443529</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>454265</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>498087</t>
+          <t>421471</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488811</t>
+          <t>413717</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505216</t>
+          <t>425746</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>947888</t>
+          <t>879668</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936604</t>
+          <t>869399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>956294</t>
+          <t>888008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,107 +6218,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9270</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3457</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7822</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3658</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>7368</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>3521</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>13573</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6316</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22132</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>9772</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>4460</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>23758</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6331,107 +6331,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>164709</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>159149</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>167453</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>146094</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>141729</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148291</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>146318</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>141925</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148556</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,63%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>311027</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>304822</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>314874</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>97,69%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>177033</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>161217</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>181649</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>323128</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>309142</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>328440</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,107 +6561,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23574</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16067</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33293</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8702</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21576</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14592</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9164</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23163</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>38166</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>28238</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>50149</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>27160</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18728</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>41195</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>41255</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>31169</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>58098</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -6674,107 +6674,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>677255</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>667536</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>684762</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>922</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>649828</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>642347</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>655221</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>613744</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>605173</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>619172</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1290999</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1279016</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1300927</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>97,88%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>734812</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>720777</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>743244</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1869</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1384640</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1367797</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1394726</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
